--- a/Test Cases for Aarong.xlsx
+++ b/Test Cases for Aarong.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bebed286a0b7e287/Attachments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bebed286a0b7e287/Documents/NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE1153A-D046-45DC-BDC4-8F669382C4FF}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6AF75D0-38BB-4D19-A363-00F339D9DDE3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sign up" sheetId="1" r:id="rId1"/>
     <sheet name="Log in" sheetId="2" r:id="rId2"/>
     <sheet name="Test Plan" sheetId="3" r:id="rId3"/>
     <sheet name="Mind Map" sheetId="4" r:id="rId4"/>
+    <sheet name="Bug Report" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -948,7 +949,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1041,6 +1042,18 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1171,7 +1184,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1224,6 +1237,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1250,7 +1264,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1367,15 +1386,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1405,7 +1424,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="57150" y="0"/>
+          <a:off x="0" y="66675"/>
           <a:ext cx="9334500" cy="7477125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1644,18 +1663,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -1753,7 +1772,7 @@
       <c r="AA3" s="5"/>
     </row>
     <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="6"/>
@@ -1783,8 +1802,8 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="21" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -1813,8 +1832,8 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="7" t="s">
         <v>25</v>
       </c>
@@ -1841,8 +1860,8 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="7" t="s">
         <v>29</v>
       </c>
@@ -1869,8 +1888,8 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -1899,8 +1918,8 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="7" t="s">
         <v>37</v>
       </c>
@@ -1927,8 +1946,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="7" t="s">
         <v>41</v>
       </c>
@@ -1955,8 +1974,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="21" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -2002,8 +2021,8 @@
       <c r="AA11" s="9"/>
     </row>
     <row r="12" spans="1:27" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="7" t="s">
         <v>48</v>
       </c>
@@ -2030,8 +2049,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="7" t="s">
         <v>52</v>
       </c>
@@ -2050,7 +2069,7 @@
       <c r="H13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="33" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="7" t="s">
@@ -2058,8 +2077,8 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="23"/>
       <c r="C14" s="7" t="s">
         <v>57</v>
       </c>
@@ -2086,8 +2105,8 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="20" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="21" t="s">
         <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -2116,8 +2135,8 @@
       </c>
     </row>
     <row r="16" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="7" t="s">
         <v>65</v>
       </c>
@@ -2144,8 +2163,8 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="7" t="s">
         <v>68</v>
       </c>
@@ -2172,8 +2191,8 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="7" t="s">
         <v>72</v>
       </c>
@@ -2200,8 +2219,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="21" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -2230,8 +2249,8 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="7" t="s">
         <v>79</v>
       </c>
@@ -2258,8 +2277,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="7" t="s">
         <v>84</v>
       </c>
@@ -2286,8 +2305,8 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
-      <c r="B22" s="20" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="21" t="s">
         <v>87</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -2316,8 +2335,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="7" t="s">
         <v>91</v>
       </c>
@@ -2342,8 +2361,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="7" t="s">
         <v>95</v>
       </c>
@@ -2370,8 +2389,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
       <c r="C25" s="7" t="s">
         <v>99</v>
       </c>
@@ -2398,8 +2417,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="7" t="s">
         <v>103</v>
       </c>
@@ -2426,8 +2445,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="20" t="s">
+      <c r="A27" s="22"/>
+      <c r="B27" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -2456,8 +2475,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
       <c r="C28" s="7" t="s">
         <v>112</v>
       </c>
@@ -2484,8 +2503,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="7" t="s">
         <v>115</v>
       </c>
@@ -2510,8 +2529,8 @@
       <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="7" t="s">
         <v>119</v>
       </c>
@@ -2536,8 +2555,8 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="22"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="23"/>
       <c r="C31" s="7" t="s">
         <v>123</v>
       </c>
@@ -2564,8 +2583,8 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="20" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="21" t="s">
         <v>126</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -2594,8 +2613,8 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
       <c r="C33" s="7" t="s">
         <v>130</v>
       </c>
@@ -2622,8 +2641,8 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="7" t="s">
         <v>134</v>
       </c>
@@ -2648,8 +2667,8 @@
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="22"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="23"/>
       <c r="C35" s="7" t="s">
         <v>136</v>
       </c>
@@ -2676,8 +2695,8 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
-      <c r="B36" s="20" t="s">
+      <c r="A36" s="22"/>
+      <c r="B36" s="21" t="s">
         <v>139</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -2706,8 +2725,8 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
-      <c r="B37" s="22"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="23"/>
       <c r="C37" s="7" t="s">
         <v>143</v>
       </c>
@@ -2734,8 +2753,8 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="25" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="26" t="s">
         <v>146</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -2764,8 +2783,8 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
       <c r="C39" s="7" t="s">
         <v>151</v>
       </c>
@@ -2792,12 +2811,12 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
       <c r="C40" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="34" t="s">
         <v>156</v>
       </c>
       <c r="E40" s="10" t="s">
@@ -2812,7 +2831,7 @@
       <c r="H40" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="33" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="7" t="s">
@@ -2820,8 +2839,8 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
       <c r="C41" s="7" t="s">
         <v>160</v>
       </c>
@@ -2840,7 +2859,7 @@
       <c r="H41" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="I41" s="33" t="s">
         <v>56</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -2848,8 +2867,8 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
       <c r="C42" s="7" t="s">
         <v>165</v>
       </c>
@@ -2876,8 +2895,8 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
       <c r="C43" s="7" t="s">
         <v>169</v>
       </c>
@@ -2927,6 +2946,7 @@
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2945,18 +2965,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
       <c r="K1" s="14"/>
       <c r="L1" s="14"/>
       <c r="M1" s="14"/>
@@ -3054,10 +3074,10 @@
       <c r="AA3" s="5"/>
     </row>
     <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="28" t="s">
         <v>75</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -3086,8 +3106,8 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="7" t="s">
         <v>177</v>
       </c>
@@ -3114,8 +3134,8 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="7" t="s">
         <v>180</v>
       </c>
@@ -3142,8 +3162,8 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="7" t="s">
         <v>182</v>
       </c>
@@ -3187,8 +3207,8 @@
       <c r="AA7" s="16"/>
     </row>
     <row r="8" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="28" t="s">
         <v>108</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -3234,8 +3254,8 @@
       <c r="AA8" s="16"/>
     </row>
     <row r="9" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="7" t="s">
         <v>189</v>
       </c>
@@ -3279,8 +3299,8 @@
       <c r="AA9" s="16"/>
     </row>
     <row r="10" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="7" t="s">
         <v>193</v>
       </c>
@@ -3324,8 +3344,8 @@
       <c r="AA10" s="16"/>
     </row>
     <row r="11" spans="1:27" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="7" t="s">
         <v>197</v>
       </c>
@@ -3369,8 +3389,8 @@
       <c r="AA11" s="16"/>
     </row>
     <row r="12" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
-      <c r="B12" s="26" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="27" t="s">
         <v>202</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -3416,15 +3436,15 @@
       <c r="AA12" s="16"/>
     </row>
     <row r="13" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="7" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="31" t="s">
         <v>208</v>
       </c>
       <c r="F13" s="10" t="s">
@@ -3461,15 +3481,15 @@
       <c r="AA13" s="16"/>
     </row>
     <row r="14" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="7" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="23"/>
       <c r="F14" s="10" t="s">
         <v>15</v>
       </c>
@@ -3504,8 +3524,8 @@
       <c r="AA14" s="16"/>
     </row>
     <row r="15" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="7" t="s">
         <v>61</v>
       </c>
@@ -3549,8 +3569,8 @@
       <c r="AA15" s="16"/>
     </row>
     <row r="16" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
-      <c r="B16" s="27" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="28" t="s">
         <v>218</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -3596,8 +3616,8 @@
       <c r="AA16" s="16"/>
     </row>
     <row r="17" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="7" t="s">
         <v>68</v>
       </c>
@@ -3641,8 +3661,8 @@
       <c r="AA17" s="16"/>
     </row>
     <row r="18" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="7" t="s">
         <v>72</v>
       </c>
@@ -3686,8 +3706,8 @@
       <c r="AA18" s="16"/>
     </row>
     <row r="19" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="7" t="s">
         <v>76</v>
       </c>
@@ -3731,8 +3751,8 @@
       <c r="AA19" s="16"/>
     </row>
     <row r="20" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="7" t="s">
         <v>79</v>
       </c>
@@ -3776,8 +3796,8 @@
       <c r="AA20" s="16"/>
     </row>
     <row r="21" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="7" t="s">
         <v>84</v>
       </c>
@@ -3819,8 +3839,8 @@
       <c r="AA21" s="16"/>
     </row>
     <row r="22" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
-      <c r="B22" s="26" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="27" t="s">
         <v>146</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -3866,8 +3886,8 @@
       <c r="AA22" s="16"/>
     </row>
     <row r="23" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="7" t="s">
         <v>91</v>
       </c>
@@ -3911,8 +3931,8 @@
       <c r="AA23" s="16"/>
     </row>
     <row r="24" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="7" t="s">
         <v>95</v>
       </c>
@@ -3956,8 +3976,8 @@
       <c r="AA24" s="16"/>
     </row>
     <row r="25" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
       <c r="C25" s="7" t="s">
         <v>99</v>
       </c>
@@ -4001,8 +4021,8 @@
       <c r="AA25" s="16"/>
     </row>
     <row r="26" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
       <c r="C26" s="7" t="s">
         <v>103</v>
       </c>
@@ -4046,8 +4066,8 @@
       <c r="AA26" s="16"/>
     </row>
     <row r="27" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="7" t="s">
         <v>109</v>
       </c>
@@ -4091,8 +4111,8 @@
       <c r="AA27" s="16"/>
     </row>
     <row r="28" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
-      <c r="B28" s="27" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="28" t="s">
         <v>232</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -4138,8 +4158,8 @@
       <c r="AA28" s="16"/>
     </row>
     <row r="29" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="7" t="s">
         <v>115</v>
       </c>
@@ -4183,8 +4203,8 @@
       <c r="AA29" s="16"/>
     </row>
     <row r="30" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
-      <c r="B30" s="22"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="23"/>
       <c r="C30" s="7" t="s">
         <v>119</v>
       </c>
@@ -4228,8 +4248,8 @@
       <c r="AA30" s="16"/>
     </row>
     <row r="31" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="27" t="s">
+      <c r="A31" s="22"/>
+      <c r="B31" s="28" t="s">
         <v>245</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -4275,8 +4295,8 @@
       <c r="AA31" s="16"/>
     </row>
     <row r="32" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
       <c r="C32" s="7" t="s">
         <v>127</v>
       </c>
@@ -4330,14 +4350,14 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="14" spans="16:21" x14ac:dyDescent="0.2">
-      <c r="P14" s="31" t="s">
+      <c r="P14" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4360,7 +4380,7 @@
   </cols>
   <sheetData>
     <row r="29" spans="17:17" x14ac:dyDescent="0.2">
-      <c r="Q29" s="32" t="s">
+      <c r="Q29" s="20" t="s">
         <v>252</v>
       </c>
     </row>
@@ -4371,4 +4391,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2AF56C-CEFE-412D-AAFB-5CEF6AF46D75}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Test Cases for Aarong.xlsx
+++ b/Test Cases for Aarong.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bebed286a0b7e287/Documents/NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2225ED80-588F-439E-AA53-9B0E37F1563C}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFAF4CE3-AD95-412E-AC4B-5AF18AB5F234}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="252">
   <si>
     <t xml:space="preserve">                                                                                                          Aarong Sign up</t>
   </si>
@@ -902,21 +902,6 @@
 redirect to error page</t>
   </si>
   <si>
-    <t>Verify login failed 
-thorugh facebook</t>
-  </si>
-  <si>
-    <t>Enter invalid Fb credentials.</t>
-  </si>
-  <si>
-    <t>System should show 
-an error message.</t>
-  </si>
-  <si>
-    <t>Fcaebook login button
- redirect to error page</t>
-  </si>
-  <si>
     <t>Google</t>
   </si>
   <si>
@@ -946,13 +931,19 @@
   </si>
   <si>
     <t>JIRA link</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>Bug Report</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1057,6 +1048,11 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1187,7 +1183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1273,6 +1269,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1457,20 +1456,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>95783</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A7E5D2-204B-DD89-56F0-7E5662C6EE6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E2F9FF4-1A81-450A-B834-EDF9BD7E57D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1486,8 +1485,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="47625"/>
-          <a:ext cx="7086600" cy="2952750"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7200900" cy="3820058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{970B1505-4336-FE82-26F7-F9F1C9E1DCCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="161925" y="3781425"/>
+          <a:ext cx="6905625" cy="3343275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3007,7 +3050,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA32"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="19" customWidth="1"/>
@@ -4211,7 +4254,7 @@
     </row>
     <row r="29" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="7" t="s">
         <v>115</v>
       </c>
@@ -4230,8 +4273,8 @@
       <c r="H29" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>56</v>
+      <c r="I29" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>15</v>
@@ -4256,27 +4299,29 @@
     </row>
     <row r="30" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="24"/>
-      <c r="B30" s="25"/>
+      <c r="B30" s="30" t="s">
+        <v>241</v>
+      </c>
       <c r="C30" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F30" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>244</v>
+        <v>24</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>15</v>
@@ -4300,25 +4345,23 @@
       <c r="AA30" s="16"/>
     </row>
     <row r="31" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="24"/>
-      <c r="B31" s="30" t="s">
-        <v>245</v>
-      </c>
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
       <c r="C31" s="7" t="s">
         <v>123</v>
       </c>
       <c r="D31" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>248</v>
-      </c>
       <c r="H31" s="7" t="s">
         <v>24</v>
       </c>
@@ -4326,69 +4369,25 @@
         <v>18</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
-      <c r="AA31" s="16"/>
-    </row>
-    <row r="32" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="7" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B22:B27"/>
-    <mergeCell ref="B28:B30"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A4:A32"/>
+    <mergeCell ref="A4:A31"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B28:B29"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I32" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I31" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4403,7 +4402,7 @@
   <sheetData>
     <row r="14" spans="16:21" x14ac:dyDescent="0.2">
       <c r="P14" s="34" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Q14" s="34"/>
       <c r="R14" s="34"/>
@@ -4433,7 +4432,7 @@
   <sheetData>
     <row r="29" spans="17:17" x14ac:dyDescent="0.2">
       <c r="Q29" s="20" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -4447,19 +4446,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2AF56C-CEFE-412D-AAFB-5CEF6AF46D75}">
-  <dimension ref="M4"/>
+  <dimension ref="M3:M28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
+    <row r="3" spans="13:13" x14ac:dyDescent="0.2">
+      <c r="M3" t="s">
+        <v>251</v>
+      </c>
+    </row>
     <row r="4" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M4" s="20" t="s">
-        <v>253</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="13:13" x14ac:dyDescent="0.2">
+      <c r="M27" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="28" spans="13:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="20" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M4" r:id="rId1" xr:uid="{B00154F1-3CF0-4A20-AA19-B2D96AFE5BA4}"/>
+    <hyperlink ref="M28" r:id="rId2" xr:uid="{4911641C-561B-4BF8-BEFC-8AA9CB5044FB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/Test Cases for Aarong.xlsx
+++ b/Test Cases for Aarong.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bebed286a0b7e287/Documents/NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFAF4CE3-AD95-412E-AC4B-5AF18AB5F234}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5755E1F3-E727-4BA3-A575-B5FD9F1198BF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sign up" sheetId="1" r:id="rId1"/>
-    <sheet name="Log in" sheetId="2" r:id="rId2"/>
+    <sheet name="Signup" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" r:id="rId2"/>
     <sheet name="Test Plan" sheetId="3" r:id="rId3"/>
     <sheet name="Mind Map" sheetId="4" r:id="rId4"/>
     <sheet name="Bug Report" sheetId="5" r:id="rId5"/>
+    <sheet name="Test senario" sheetId="6" r:id="rId6"/>
+    <sheet name="RTM" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="352">
   <si>
     <t xml:space="preserve">                                                                                                          Aarong Sign up</t>
   </si>
@@ -938,12 +940,338 @@
   <si>
     <t>Bug Report</t>
   </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Created By</t>
+  </si>
+  <si>
+    <t>Test Scenario ID</t>
+  </si>
+  <si>
+    <t>Test Scenario Description</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Number of Test Cases</t>
+  </si>
+  <si>
+    <t>TS01</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>TS02</t>
+  </si>
+  <si>
+    <t>TS03</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>TS04</t>
+  </si>
+  <si>
+    <t>TS05</t>
+  </si>
+  <si>
+    <t>TS06</t>
+  </si>
+  <si>
+    <t>TS07</t>
+  </si>
+  <si>
+    <t>TS08</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>TS09</t>
+  </si>
+  <si>
+    <t>TS10</t>
+  </si>
+  <si>
+    <t>TS11</t>
+  </si>
+  <si>
+    <t>Validate Terms &amp; Conditions acceptance</t>
+  </si>
+  <si>
+    <t>TS12</t>
+  </si>
+  <si>
+    <t>TS13</t>
+  </si>
+  <si>
+    <t>4 (Login TC1-TC4)</t>
+  </si>
+  <si>
+    <t>TS14</t>
+  </si>
+  <si>
+    <t>4 (Login TC5-TC8)</t>
+  </si>
+  <si>
+    <t>TS15</t>
+  </si>
+  <si>
+    <t>4 (Login TC9-TC12)</t>
+  </si>
+  <si>
+    <t>TS16</t>
+  </si>
+  <si>
+    <t>6 (Login TC13-TC18)</t>
+  </si>
+  <si>
+    <t>TS17</t>
+  </si>
+  <si>
+    <t>6 (Login TC19-TC24)</t>
+  </si>
+  <si>
+    <t>TS18</t>
+  </si>
+  <si>
+    <t>2 (Login TC25-TC26)</t>
+  </si>
+  <si>
+    <t>2 (Login TC27-TC28)</t>
+  </si>
+  <si>
+    <t>1 (SignUp TC01)</t>
+  </si>
+  <si>
+    <t>3 (SignUpTC02, TC03, TC04)</t>
+  </si>
+  <si>
+    <t>3 (SignUp TC05, TC06, TC07)</t>
+  </si>
+  <si>
+    <t>3 (SignUpTC16, TC17, TC18)</t>
+  </si>
+  <si>
+    <t>2 (SignUp TC33, TC34)</t>
+  </si>
+  <si>
+    <t>Validate Phone Number field in Sign up 
+(valid, invalid, max length, empty)</t>
+  </si>
+  <si>
+    <t>Validate Gender selection 
+(male, female, others, none)</t>
+  </si>
+  <si>
+    <t>Validate Last Name field
+ (valid, invalid, empty)</t>
+  </si>
+  <si>
+    <t>Validate First Name field 
+(valid, invalid, empty)</t>
+  </si>
+  <si>
+    <t>Validate Email field in Sign up 
+(valid, invalid domain, empty)</t>
+  </si>
+  <si>
+    <t>Validate Password field 
+(valid, invalid, strong, icon, empty)</t>
+  </si>
+  <si>
+    <t>Validate Confirm Password field
+ (match, mismatch, icon, empty)</t>
+  </si>
+  <si>
+    <t>Validate OTP functionality in Sign up 
+(valid, invalid, expiry, resend, empty)</t>
+  </si>
+  <si>
+    <t>Validate Login – Email field
+(valid, invalid, empty, uppercase)</t>
+  </si>
+  <si>
+    <t>Validate Forgot Password functionality 
+(link, email notification, reset page, token)</t>
+  </si>
+  <si>
+    <t>Validate Login – Password field
+ (wrong, correct, empty, visibility)</t>
+  </si>
+  <si>
+    <t>Validate Login – OTP functionality 
+(valid, wrong, expiry, resend, empty)</t>
+  </si>
+  <si>
+    <t>6 (SignUp TC35, TC36, TC37,
+ TC38, TC39, TC40)</t>
+  </si>
+  <si>
+    <t>5 (SignUp TC24, TC25, TC26, 
+TC27, TC28)</t>
+  </si>
+  <si>
+    <t>5 ( SignUpTC19, TC20, TC21, 
+TC22, TC23)</t>
+  </si>
+  <si>
+    <t>4 (SignUp TC29, TC30,
+TC31, TC32)</t>
+  </si>
+  <si>
+    <t>Validate Login – Phone number field 
+(valid, invalid, length, 
+max 11 digits, unregistered, empty)</t>
+  </si>
+  <si>
+    <t>4 (SignUpTC08, TC09, TC10, 
+TC11)</t>
+  </si>
+  <si>
+    <t>4 (SignUpTC12, TC13, TC14,
+TC15)</t>
+  </si>
+  <si>
+    <t>Validate Social login-
+Google (success, cancel)</t>
+  </si>
+  <si>
+    <t>Validate Social login-
+Facebook (success, cancel)</t>
+  </si>
+  <si>
+    <t>Verify Sign up page navigation
+ and accessibility</t>
+  </si>
+  <si>
+    <t>Validate Date of Birth field 
+(valid date, arrows, month, year, 
+future date)</t>
+  </si>
+  <si>
+    <t>Aarong</t>
+  </si>
+  <si>
+    <t>Afia Anjum</t>
+  </si>
+  <si>
+    <t>Test Metrics</t>
+  </si>
+  <si>
+    <t>#SL</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Result (%)</t>
+  </si>
+  <si>
+    <t>Percentage of Test Cases Executed</t>
+  </si>
+  <si>
+    <t>(No. of Test Cases Executed / Total no. of Test Cases Written) * 100</t>
+  </si>
+  <si>
+    <t>Percentage of Test Cases Not Executed</t>
+  </si>
+  <si>
+    <t>(No. of Test Cases not Executed / Total no. of Test Cases Written) * 100</t>
+  </si>
+  <si>
+    <t>Percentage of Test Cases Passed</t>
+  </si>
+  <si>
+    <t>(No. of Test Cases Passed / Total no. of Test Cases Executed) * 100</t>
+  </si>
+  <si>
+    <t>Percentage of Test Cases Failed</t>
+  </si>
+  <si>
+    <t>(No. of Test Cases Failed / Total no. of Test Cases Executed) * 100</t>
+  </si>
+  <si>
+    <t>Percentage of Test Cases Blocked</t>
+  </si>
+  <si>
+    <t>(No. of Test Cases Blocked / Total no. of Test Cases Executed) * 100</t>
+  </si>
+  <si>
+    <t>Defect Density</t>
+  </si>
+  <si>
+    <t>No. of Defects found / Size (No. of Requirements)</t>
+  </si>
+  <si>
+    <t>Defect Removal Efficiency (DRE)</t>
+  </si>
+  <si>
+    <t>(Fixed Defects / (Fixed Defects + Missed Defects)) * 100</t>
+  </si>
+  <si>
+    <t>Defect Leakage</t>
+  </si>
+  <si>
+    <t>(No. of Defects found in UAT/ No. of Defects found in Testing) * 100</t>
+  </si>
+  <si>
+    <t>Defect Rejection Ratio</t>
+  </si>
+  <si>
+    <t>(No. of Defects Rejected/ Total no. of Defects Raised) * 100</t>
+  </si>
+  <si>
+    <t>Defect Age</t>
+  </si>
+  <si>
+    <t>Fixed date - Reported date</t>
+  </si>
+  <si>
+    <t>Customer Satisfaction</t>
+  </si>
+  <si>
+    <t>No. of complaints per Period of Time</t>
+  </si>
+  <si>
+    <t>(65/65)*100 = 100</t>
+  </si>
+  <si>
+    <t>(0/65)*100 = 0</t>
+  </si>
+  <si>
+    <t>(54/60)*100 = 90%</t>
+  </si>
+  <si>
+    <t>(11/65)*100 = 17%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Requirements Traceability Matrix for Aarong (Signup &amp; Login)</t>
+  </si>
+  <si>
+    <t>Should show an 
+error.</t>
+  </si>
+  <si>
+    <t>Verify that phone number field accepts maximum 11 digits only.</t>
+  </si>
+  <si>
+    <t>Clicking “Didn’t receive the OTP?” does not perform any action</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -979,12 +1307,6 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -998,13 +1320,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1054,8 +1369,145 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1080,8 +1532,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.34998626667073579"/>
+        <bgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
+        <bgColor rgb="FFF4B083"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor rgb="FF548135"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1178,14 +1660,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1197,15 +1732,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1214,7 +1743,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1229,53 +1758,149 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{515DDDD8-80D1-445B-9207-FFB6045BA61E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{71F55507-54D1-4E38-9783-6697D87CAC24}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1751,1269 +2376,1268 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="7" max="8" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-    </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+    </row>
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-    </row>
-    <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="K3" s="3"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+    </row>
+    <row r="4" spans="1:27" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="24"/>
-      <c r="B5" s="23" t="s">
+      <c r="J4" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="25"/>
+      <c r="B5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="7" t="s">
+      <c r="J5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="7" t="s">
+      <c r="J6" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="25"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="24"/>
-      <c r="B8" s="23" t="s">
+      <c r="J7" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="25"/>
+      <c r="B8" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="7" t="s">
+      <c r="J8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="7" t="s">
+      <c r="J9" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="23" t="s">
+      <c r="J10" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="25"/>
+      <c r="B11" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="F11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-    </row>
-    <row r="12" spans="1:27" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="7" t="s">
+      <c r="J11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+    </row>
+    <row r="12" spans="1:27" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="F12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="7" t="s">
+      <c r="J12" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="7" t="s">
+      <c r="J13" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="23" t="s">
+      <c r="J14" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="25"/>
+      <c r="B15" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="7" t="s">
+      <c r="J15" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="7" t="s">
+      <c r="J16" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="7" t="s">
+      <c r="J17" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="F18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="23" t="s">
+      <c r="J18" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="7" t="s">
+      <c r="F19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="7" t="s">
+      <c r="J19" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="7" t="s">
+      <c r="F20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="7" t="s">
+      <c r="J20" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="7" t="s">
+      <c r="F21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="24"/>
-      <c r="B22" s="23" t="s">
+      <c r="J21" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="25"/>
+      <c r="B22" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="7" t="s">
+      <c r="F22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="7" t="s">
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7" t="s">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="7" t="s">
+      <c r="J23" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="7" t="s">
+      <c r="F24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="7" t="s">
+      <c r="J24" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="7" t="s">
+      <c r="F25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="7" t="s">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="11" t="s">
+      <c r="F26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
-      <c r="B27" s="23" t="s">
+      <c r="J26" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="25"/>
+      <c r="B27" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="F27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="7" t="s">
+      <c r="J27" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="19" t="s">
+      <c r="F28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="7" t="s">
+      <c r="J28" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="7" t="s">
+      <c r="F29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="7"/>
-    </row>
-    <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="7" t="s">
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="7" t="s">
+      <c r="F30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="7"/>
-    </row>
-    <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="24"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="7" t="s">
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="25"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="7" t="s">
+      <c r="F31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="24"/>
-      <c r="B32" s="23" t="s">
+      <c r="J31" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A32" s="25"/>
+      <c r="B32" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="7" t="s">
+      <c r="F32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J32" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="7" t="s">
+      <c r="J32" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="7" t="s">
+      <c r="F33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="7" t="s">
+      <c r="A34" s="25"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="7" t="s">
+      <c r="F34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I34" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="7"/>
-    </row>
-    <row r="35" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="7" t="s">
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="7" t="s">
+      <c r="F35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="24"/>
-      <c r="B36" s="23" t="s">
+      <c r="J35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A36" s="25"/>
+      <c r="B36" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="F36" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="7" t="s">
+      <c r="F36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J36" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A37" s="24"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="7" t="s">
+      <c r="A37" s="25"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="F37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I37" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="J37" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A38" s="24"/>
-      <c r="B38" s="28" t="s">
+      <c r="A38" s="25"/>
+      <c r="B38" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="10" t="s">
+      <c r="F38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I38" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J38" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="7" t="s">
+      <c r="A39" s="25"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F39" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="F39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="I39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J39" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="7" t="s">
+      <c r="J39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A40" s="25"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="10" t="s">
+      <c r="F40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="I40" s="21" t="s">
+      <c r="I40" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="7" t="s">
+      <c r="A41" s="25"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="F41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="I41" s="21" t="s">
+      <c r="I41" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="J41" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="24"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="7" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F42" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" s="10" t="s">
+      <c r="F42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I42" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="7" t="s">
+      <c r="J42" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" s="7" t="s">
+      <c r="F43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I43" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3053,1322 +3677,1324 @@
   <dimension ref="A1:AA31"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
     </row>
     <row r="2" spans="1:27" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
     </row>
     <row r="3" spans="1:27" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-    </row>
-    <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+      <c r="K3" s="3"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+    </row>
+    <row r="4" spans="1:27" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="60" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="7" t="s">
+      <c r="J4" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="61"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="7" t="s">
+      <c r="J5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="61"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="7" t="s">
+      <c r="J6" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="61"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="F7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-    </row>
-    <row r="8" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="24"/>
-      <c r="B8" s="30" t="s">
+      <c r="J7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+    </row>
+    <row r="8" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="61"/>
+      <c r="B8" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="10" t="s">
+      <c r="F8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="16"/>
+      <c r="J8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
     </row>
     <row r="9" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="7" t="s">
+      <c r="A9" s="61"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
+      <c r="J9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
     </row>
     <row r="10" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="10" t="s">
+      <c r="F10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
+      <c r="J10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
     </row>
     <row r="11" spans="1:27" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="61"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
+      <c r="J11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
     </row>
     <row r="12" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="24"/>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="61"/>
+      <c r="B12" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-    </row>
-    <row r="13" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="7" t="s">
+      <c r="J12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+    </row>
+    <row r="13" spans="1:27" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="61"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-    </row>
-    <row r="14" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="7" t="s">
+      <c r="J13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+    </row>
+    <row r="14" spans="1:27" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="61"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="E14" s="58"/>
+      <c r="F14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="16"/>
+      <c r="J14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
     </row>
     <row r="15" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="7" t="s">
+      <c r="A15" s="61"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
+      <c r="J15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
     </row>
     <row r="16" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="30" t="s">
+      <c r="A16" s="61"/>
+      <c r="B16" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
+      <c r="J16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="13"/>
     </row>
     <row r="17" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="7" t="s">
+      <c r="A17" s="61"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="F17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
+      <c r="J17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
     </row>
     <row r="18" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="7" t="s">
+      <c r="A18" s="61"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="10" t="s">
+      <c r="F18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-    </row>
-    <row r="19" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="7" t="s">
+      <c r="J18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+    </row>
+    <row r="19" spans="1:27" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" s="61"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="D19" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="7" t="s">
+      <c r="F19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="H19" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16"/>
+      <c r="J19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
     </row>
     <row r="20" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="7" t="s">
+      <c r="A20" s="61"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="10" t="s">
+      <c r="F20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-      <c r="AA20" s="16"/>
+      <c r="J20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
     </row>
     <row r="21" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="7" t="s">
+      <c r="A21" s="61"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="57" t="s">
         <v>229</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="10" t="s">
+      <c r="F21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="16"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="16"/>
+      <c r="J21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
     </row>
     <row r="22" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="24"/>
-      <c r="B22" s="29" t="s">
+      <c r="A22" s="61"/>
+      <c r="B22" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="10" t="s">
+      <c r="F22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
-      <c r="AA22" s="16"/>
+      <c r="J22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
     </row>
     <row r="23" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="7" t="s">
+      <c r="A23" s="61"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="F23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="16"/>
-      <c r="Z23" s="16"/>
-      <c r="AA23" s="16"/>
-    </row>
-    <row r="24" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="7" t="s">
+      <c r="J23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+    </row>
+    <row r="24" spans="1:27" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="61"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="10" t="s">
+      <c r="F24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="Y24" s="16"/>
-      <c r="Z24" s="16"/>
-      <c r="AA24" s="16"/>
-    </row>
-    <row r="25" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="7" t="s">
+      <c r="J24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+    </row>
+    <row r="25" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="61"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="10" t="s">
+      <c r="F25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="I25" s="7" t="s">
+      <c r="H25" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="I25" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="16"/>
-    </row>
-    <row r="26" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="7" t="s">
+      <c r="J25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+    </row>
+    <row r="26" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="61"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="10" t="s">
+      <c r="F26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
-      <c r="Z26" s="16"/>
-      <c r="AA26" s="16"/>
-    </row>
-    <row r="27" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="7" t="s">
+      <c r="J26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+    </row>
+    <row r="27" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="61"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="F27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
-      <c r="Z27" s="16"/>
-      <c r="AA27" s="16"/>
-    </row>
-    <row r="28" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="24"/>
-      <c r="B28" s="30" t="s">
+      <c r="J27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+    </row>
+    <row r="28" spans="1:27" ht="51" x14ac:dyDescent="0.2">
+      <c r="A28" s="61"/>
+      <c r="B28" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="7" t="s">
+      <c r="F28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-    </row>
-    <row r="29" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
+      <c r="J28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+    </row>
+    <row r="29" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="61"/>
       <c r="B29" s="35"/>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="7" t="s">
+      <c r="F29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="16"/>
-    </row>
-    <row r="30" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="24"/>
-      <c r="B30" s="30" t="s">
+      <c r="J29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+    </row>
+    <row r="30" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="61"/>
+      <c r="B30" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="7" t="s">
+      <c r="F30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="16"/>
-    </row>
-    <row r="31" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="7" t="s">
+      <c r="J30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="13"/>
+    </row>
+    <row r="31" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="62"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="7" t="s">
+      <c r="F31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4385,7 +5011,7 @@
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B28:B29"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I31" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Pass,Fail"</formula1>
@@ -4401,14 +5027,14 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="14" spans="16:21" x14ac:dyDescent="0.2">
-      <c r="P14" s="34" t="s">
+      <c r="P14" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4431,7 +5057,7 @@
   </cols>
   <sheetData>
     <row r="29" spans="17:17" x14ac:dyDescent="0.2">
-      <c r="Q29" s="20" t="s">
+      <c r="Q29" s="15" t="s">
         <v>248</v>
       </c>
     </row>
@@ -4458,7 +5084,7 @@
       </c>
     </row>
     <row r="4" spans="13:13" x14ac:dyDescent="0.2">
-      <c r="M4" s="20" t="s">
+      <c r="M4" s="15" t="s">
         <v>249</v>
       </c>
     </row>
@@ -4468,7 +5094,7 @@
       </c>
     </row>
     <row r="28" spans="13:13" x14ac:dyDescent="0.2">
-      <c r="M28" s="20" t="s">
+      <c r="M28" s="15" t="s">
         <v>250</v>
       </c>
     </row>
@@ -4480,4 +5106,547 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394FA0E8-94A9-43C2-B064-2A252E97FB14}">
+  <dimension ref="A1:Y23"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="37"/>
+      <c r="B1" s="38"/>
+    </row>
+    <row r="2" spans="1:25" s="47" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+    </row>
+    <row r="3" spans="1:25" s="47" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="18"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
+      <c r="Y5" s="18"/>
+    </row>
+    <row r="6" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A10" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A11" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.2">
+      <c r="A12" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A13" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A14" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.2">
+      <c r="A16" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A18" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A19" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+      <c r="A20" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A21" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A22" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>312</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A23" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="21" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F7E3F6-51AE-45A2-985D-B36379FBF555}">
+  <dimension ref="B1:E16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="4" max="4" width="72.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="56" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="54" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+    </row>
+    <row r="5" spans="2:5" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="B5" s="53" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>319</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B6" s="48">
+        <v>1</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B7" s="48">
+        <v>2</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="48">
+        <v>3</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="48">
+        <v>4</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>329</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B10" s="48">
+        <v>5</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="48">
+        <v>6</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>332</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B12" s="48">
+        <v>7</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B13" s="48">
+        <v>8</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>337</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B14" s="48">
+        <v>9</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B15" s="48">
+        <v>10</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>341</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B16" s="48">
+        <v>11</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:E4"/>
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>